--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1287,7 +1287,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121753743</v>
+        <v>121753760</v>
       </c>
       <c r="B7" t="n">
         <v>57373</v>
@@ -1321,24 +1321,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694434</v>
+        <v>694445</v>
       </c>
       <c r="R7" t="n">
-        <v>6658762</v>
+        <v>6658760</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1509,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121753760</v>
+        <v>121765721</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>97069</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,43 +1518,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>224363</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694445</v>
+        <v>694517</v>
       </c>
       <c r="R9" t="n">
-        <v>6658760</v>
+        <v>6658684</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1598,28 +1590,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Tallmosse/sumpskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121753973</v>
+        <v>121761316</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,46 +1626,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694528</v>
+        <v>694505</v>
       </c>
       <c r="R10" t="n">
-        <v>6658686</v>
+        <v>6658779</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,11 +1695,21 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1707,26 +1718,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121761316</v>
+        <v>121753973</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,49 +1751,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>694505</v>
+        <v>694528</v>
       </c>
       <c r="R11" t="n">
-        <v>6658779</v>
+        <v>6658686</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,21 +1817,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1827,28 +1830,23 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121765721</v>
+        <v>121762198</v>
       </c>
       <c r="B12" t="n">
         <v>97069</v>
@@ -1884,17 +1882,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694517</v>
+        <v>694507</v>
       </c>
       <c r="R12" t="n">
-        <v>6658684</v>
+        <v>6658692</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,9 +1919,19 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,28 +1946,28 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121762198</v>
+        <v>121753975</v>
       </c>
       <c r="B13" t="n">
-        <v>97069</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1972,37 +1980,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224363</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694507</v>
+        <v>694530</v>
       </c>
       <c r="R13" t="n">
-        <v>6658692</v>
+        <v>6658683</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,19 +2046,9 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,30 +2061,25 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121753975</v>
+        <v>121753743</v>
       </c>
       <c r="B14" t="n">
-        <v>5193</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,20 +2088,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2108,12 +2110,11 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2123,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694530</v>
+        <v>694434</v>
       </c>
       <c r="R14" t="n">
-        <v>6658683</v>
+        <v>6658762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,7 +2168,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121761311</v>
+        <v>121761316</v>
       </c>
       <c r="B6" t="n">
-        <v>57248</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,16 +1173,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694395</v>
+        <v>694505</v>
       </c>
       <c r="R6" t="n">
-        <v>6658801</v>
+        <v>6658779</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1251,11 +1251,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,7 +1282,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121753760</v>
+        <v>121765718</v>
       </c>
       <c r="B7" t="n">
         <v>57373</v>
@@ -1321,21 +1316,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694445</v>
+        <v>694515</v>
       </c>
       <c r="R7" t="n">
-        <v>6658760</v>
+        <v>6658790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,6 +1360,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stort, brett hål nära tallens bas.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1378,26 +1373,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121765718</v>
+        <v>121765721</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>97069</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,38 +1406,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>224363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694515</v>
+        <v>694517</v>
       </c>
       <c r="R8" t="n">
-        <v>6658790</v>
+        <v>6658684</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,23 +1472,19 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stort, brett hål nära tallens bas.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
+          <t>Tallmosse/sumpskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1506,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121765721</v>
+        <v>121761311</v>
       </c>
       <c r="B9" t="n">
-        <v>97069</v>
+        <v>57248</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,41 +1514,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224363</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Accipiter gentilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694517</v>
+        <v>694395</v>
       </c>
       <c r="R9" t="n">
-        <v>6658684</v>
+        <v>6658801</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1579,42 +1583,56 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121761316</v>
+        <v>121753743</v>
       </c>
       <c r="B10" t="n">
         <v>57373</v>
@@ -1652,23 +1670,23 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694505</v>
+        <v>694434</v>
       </c>
       <c r="R10" t="n">
-        <v>6658779</v>
+        <v>6658762</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1695,21 +1713,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1718,31 +1726,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121753973</v>
+        <v>121762198</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>97069</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,42 +1758,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>224363</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>694528</v>
+        <v>694507</v>
       </c>
       <c r="R11" t="n">
-        <v>6658686</v>
+        <v>6658692</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1817,39 +1815,55 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121762198</v>
+        <v>121753973</v>
       </c>
       <c r="B12" t="n">
-        <v>97069</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,37 +1876,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224363</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694507</v>
+        <v>694528</v>
       </c>
       <c r="R12" t="n">
-        <v>6658692</v>
+        <v>6658686</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1919,45 +1938,29 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2076,7 +2079,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121753743</v>
+        <v>121753760</v>
       </c>
       <c r="B14" t="n">
         <v>57373</v>
@@ -2110,24 +2113,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694434</v>
+        <v>694445</v>
       </c>
       <c r="R14" t="n">
-        <v>6658762</v>
+        <v>6658760</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,6 +2183,123 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121857707</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>694330</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6658794</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1394,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121765721</v>
+        <v>121761311</v>
       </c>
       <c r="B8" t="n">
-        <v>97069</v>
+        <v>57248</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,41 +1406,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224363</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Accipiter gentilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694517</v>
+        <v>694395</v>
       </c>
       <c r="R8" t="n">
-        <v>6658684</v>
+        <v>6658801</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,45 +1475,59 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121761311</v>
+        <v>121765721</v>
       </c>
       <c r="B9" t="n">
-        <v>57248</v>
+        <v>97069</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,49 +1536,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>224363</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694395</v>
+        <v>694517</v>
       </c>
       <c r="R9" t="n">
-        <v>6658801</v>
+        <v>6658684</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,49 +1597,35 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Tallmosse</t>
+          <t>Tallmosse/sumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1157,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121761316</v>
+        <v>121765718</v>
       </c>
       <c r="B6" t="n">
         <v>57373</v>
@@ -1191,27 +1191,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694505</v>
+        <v>694515</v>
       </c>
       <c r="R6" t="n">
-        <v>6658779</v>
+        <v>6658790</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,19 +1230,14 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:55</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stort, brett hål nära tallens bas.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,25 +1251,25 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Tallmosse</t>
+          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121765718</v>
+        <v>121761316</v>
       </c>
       <c r="B7" t="n">
         <v>57373</v>
@@ -1316,19 +1303,27 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694515</v>
+        <v>694505</v>
       </c>
       <c r="R7" t="n">
-        <v>6658790</v>
+        <v>6658779</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,14 +1350,19 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Stort, brett hål nära tallens bas.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,28 +1376,28 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121761311</v>
+        <v>121765721</v>
       </c>
       <c r="B8" t="n">
-        <v>57248</v>
+        <v>97069</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,49 +1406,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>224363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694395</v>
+        <v>694517</v>
       </c>
       <c r="R8" t="n">
-        <v>6658801</v>
+        <v>6658684</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,59 +1467,45 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Tallmosse</t>
+          <t>Tallmosse/sumpskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121765721</v>
+        <v>121753760</v>
       </c>
       <c r="B9" t="n">
-        <v>97069</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1536,38 +1514,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694517</v>
+        <v>694445</v>
       </c>
       <c r="R9" t="n">
-        <v>6658684</v>
+        <v>6658760</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,34 +1591,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Tallmosse/sumpskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121753743</v>
+        <v>121753975</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,20 +1621,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1666,11 +1643,12 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1680,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694434</v>
+        <v>694530</v>
       </c>
       <c r="R10" t="n">
-        <v>6658762</v>
+        <v>6658683</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,6 +1702,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1742,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121762198</v>
+        <v>121753743</v>
       </c>
       <c r="B11" t="n">
-        <v>97069</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,41 +1733,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>694507</v>
+        <v>694434</v>
       </c>
       <c r="R11" t="n">
-        <v>6658692</v>
+        <v>6658762</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1815,55 +1802,39 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121753973</v>
+        <v>121761311</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>57248</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1872,46 +1843,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694528</v>
+        <v>694395</v>
       </c>
       <c r="R12" t="n">
-        <v>6658686</v>
+        <v>6658801</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,11 +1912,26 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1951,26 +1940,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121753975</v>
+        <v>121753973</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,43 +1977,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694530</v>
+        <v>694528</v>
       </c>
       <c r="R13" t="n">
-        <v>6658683</v>
+        <v>6658686</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2050,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2079,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121753760</v>
+        <v>121762198</v>
       </c>
       <c r="B14" t="n">
-        <v>57373</v>
+        <v>97069</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,46 +2080,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>224363</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694445</v>
+        <v>694507</v>
       </c>
       <c r="R14" t="n">
-        <v>6658760</v>
+        <v>6658692</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,29 +2141,45 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121765718</v>
+        <v>121765721</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>97069</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,38 +1169,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>224363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694515</v>
+        <v>694517</v>
       </c>
       <c r="R6" t="n">
-        <v>6658790</v>
+        <v>6658684</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,23 +1235,19 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stort, brett hål nära tallens bas.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
+          <t>Tallmosse/sumpskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1269,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121761316</v>
+        <v>121761311</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>57248</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,16 +1281,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1317,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694505</v>
+        <v>694395</v>
       </c>
       <c r="R7" t="n">
-        <v>6658779</v>
+        <v>6658801</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1363,6 +1359,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121765721</v>
+        <v>121753760</v>
       </c>
       <c r="B8" t="n">
-        <v>97069</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,38 +1407,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694517</v>
+        <v>694445</v>
       </c>
       <c r="R8" t="n">
-        <v>6658684</v>
+        <v>6658760</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,31 +1484,25 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Tallmosse/sumpskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121753760</v>
+        <v>121761316</v>
       </c>
       <c r="B9" t="n">
         <v>57373</v>
@@ -1536,24 +1536,27 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694445</v>
+        <v>694505</v>
       </c>
       <c r="R9" t="n">
-        <v>6658760</v>
+        <v>6658779</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1580,11 +1583,21 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1593,26 +1606,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121753975</v>
+        <v>121762198</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>97069</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,46 +1643,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>224363</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694530</v>
+        <v>694507</v>
       </c>
       <c r="R10" t="n">
-        <v>6658683</v>
+        <v>6658692</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,9 +1700,19 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,25 +1725,30 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121753743</v>
+        <v>121753973</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,46 +1757,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>694434</v>
+        <v>694528</v>
       </c>
       <c r="R11" t="n">
-        <v>6658762</v>
+        <v>6658686</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121761311</v>
+        <v>121753743</v>
       </c>
       <c r="B12" t="n">
-        <v>57248</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,16 +1868,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1869,23 +1890,23 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694395</v>
+        <v>694434</v>
       </c>
       <c r="R12" t="n">
-        <v>6658801</v>
+        <v>6658762</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,26 +1933,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1940,31 +1946,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121753973</v>
+        <v>121765718</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>57373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,43 +1974,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694528</v>
+        <v>694515</v>
       </c>
       <c r="R13" t="n">
-        <v>6658686</v>
+        <v>6658790</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2044,6 +2040,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stort, brett hål nära tallens bas.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2052,26 +2053,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121762198</v>
+        <v>121753975</v>
       </c>
       <c r="B14" t="n">
-        <v>97069</v>
+        <v>5193</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,37 +2090,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224363</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694507</v>
+        <v>694530</v>
       </c>
       <c r="R14" t="n">
-        <v>6658692</v>
+        <v>6658683</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2141,19 +2156,9 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,20 +2171,15 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1157,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121765721</v>
+        <v>121762198</v>
       </c>
       <c r="B6" t="n">
         <v>97069</v>
@@ -1193,17 +1193,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694517</v>
+        <v>694507</v>
       </c>
       <c r="R6" t="n">
-        <v>6658684</v>
+        <v>6658692</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,9 +1230,19 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,28 +1257,28 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121761311</v>
+        <v>121753973</v>
       </c>
       <c r="B7" t="n">
-        <v>57248</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,49 +1287,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694395</v>
+        <v>694528</v>
       </c>
       <c r="R7" t="n">
-        <v>6658801</v>
+        <v>6658686</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,26 +1353,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1374,31 +1366,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121753760</v>
+        <v>121761311</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>57248</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,16 +1398,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1429,24 +1416,27 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694445</v>
+        <v>694395</v>
       </c>
       <c r="R8" t="n">
-        <v>6658760</v>
+        <v>6658801</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,11 +1463,26 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1486,26 +1491,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121761316</v>
+        <v>121753975</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,20 +1524,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1536,27 +1546,28 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694505</v>
+        <v>694530</v>
       </c>
       <c r="R9" t="n">
-        <v>6658779</v>
+        <v>6658683</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,51 +1594,37 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121762198</v>
+        <v>121765721</v>
       </c>
       <c r="B10" t="n">
         <v>97069</v>
@@ -1663,17 +1660,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694507</v>
+        <v>694517</v>
       </c>
       <c r="R10" t="n">
-        <v>6658692</v>
+        <v>6658684</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,19 +1697,9 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,28 +1714,28 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallmosse/sumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121753973</v>
+        <v>121765718</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,43 +1744,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>694528</v>
+        <v>694515</v>
       </c>
       <c r="R11" t="n">
-        <v>6658686</v>
+        <v>6658790</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,6 +1810,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Stort, brett hål nära tallens bas.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1836,23 +1823,28 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121753743</v>
+        <v>121761316</v>
       </c>
       <c r="B12" t="n">
         <v>57373</v>
@@ -1890,23 +1882,23 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694434</v>
+        <v>694505</v>
       </c>
       <c r="R12" t="n">
-        <v>6658762</v>
+        <v>6658779</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1933,11 +1925,21 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1946,23 +1948,28 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121765718</v>
+        <v>121753760</v>
       </c>
       <c r="B13" t="n">
         <v>57373</v>
@@ -1996,16 +2003,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694515</v>
+        <v>694445</v>
       </c>
       <c r="R13" t="n">
-        <v>6658790</v>
+        <v>6658760</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,11 +2052,6 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Stort, brett hål nära tallens bas.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2053,31 +2060,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121753975</v>
+        <v>121753743</v>
       </c>
       <c r="B14" t="n">
-        <v>5193</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,20 +2088,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2108,12 +2110,11 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2123,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694530</v>
+        <v>694434</v>
       </c>
       <c r="R14" t="n">
-        <v>6658683</v>
+        <v>6658762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,7 +2168,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121762198</v>
+        <v>121753975</v>
       </c>
       <c r="B6" t="n">
-        <v>97069</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,37 +1173,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224363</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694507</v>
+        <v>694530</v>
       </c>
       <c r="R6" t="n">
-        <v>6658692</v>
+        <v>6658683</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,19 +1239,9 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,30 +1254,25 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121753973</v>
+        <v>121765721</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>97069</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,39 +1285,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>224363</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694528</v>
+        <v>694517</v>
       </c>
       <c r="R7" t="n">
-        <v>6658686</v>
+        <v>6658684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,28 +1353,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Tallmosse/sumpskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121761311</v>
+        <v>121753743</v>
       </c>
       <c r="B8" t="n">
-        <v>57248</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,16 +1393,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1420,23 +1415,23 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694395</v>
+        <v>694434</v>
       </c>
       <c r="R8" t="n">
-        <v>6658801</v>
+        <v>6658762</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,26 +1458,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1491,31 +1471,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121753975</v>
+        <v>121762198</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>97069</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,46 +1503,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>224363</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694530</v>
+        <v>694507</v>
       </c>
       <c r="R9" t="n">
-        <v>6658683</v>
+        <v>6658692</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,9 +1560,19 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,25 +1585,30 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121765721</v>
+        <v>121765718</v>
       </c>
       <c r="B10" t="n">
-        <v>97069</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,38 +1617,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694517</v>
+        <v>694515</v>
       </c>
       <c r="R10" t="n">
-        <v>6658684</v>
+        <v>6658790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1702,19 +1683,23 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stort, brett hål nära tallens bas.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog</t>
+          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1732,7 +1717,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121765718</v>
+        <v>121753760</v>
       </c>
       <c r="B11" t="n">
         <v>57373</v>
@@ -1766,16 +1751,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>694515</v>
+        <v>694445</v>
       </c>
       <c r="R11" t="n">
-        <v>6658790</v>
+        <v>6658760</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,11 +1800,6 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Stort, brett hål nära tallens bas.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1823,31 +1808,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121761316</v>
+        <v>121761311</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>57248</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,16 +1840,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1892,10 +1872,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694505</v>
+        <v>694395</v>
       </c>
       <c r="R12" t="n">
-        <v>6658779</v>
+        <v>6658801</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1938,6 +1918,11 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121753760</v>
+        <v>121753973</v>
       </c>
       <c r="B13" t="n">
-        <v>57373</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,31 +1966,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2014,10 +1999,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694445</v>
+        <v>694528</v>
       </c>
       <c r="R13" t="n">
-        <v>6658760</v>
+        <v>6658686</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,7 +2061,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121753743</v>
+        <v>121761316</v>
       </c>
       <c r="B14" t="n">
         <v>57373</v>
@@ -2114,23 +2099,23 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694434</v>
+        <v>694505</v>
       </c>
       <c r="R14" t="n">
-        <v>6658762</v>
+        <v>6658779</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,11 +2142,21 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2170,16 +2165,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>121759133</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121753975</v>
+        <v>121762198</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>97087</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,46 +1173,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>224363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694530</v>
+        <v>694507</v>
       </c>
       <c r="R6" t="n">
-        <v>6658683</v>
+        <v>6658692</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,9 +1230,19 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,25 +1255,30 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121765721</v>
+        <v>121753743</v>
       </c>
       <c r="B7" t="n">
-        <v>97069</v>
+        <v>57381</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,38 +1287,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694517</v>
+        <v>694434</v>
       </c>
       <c r="R7" t="n">
-        <v>6658684</v>
+        <v>6658762</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,34 +1367,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Tallmosse/sumpskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121753743</v>
+        <v>121753973</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,46 +1397,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694434</v>
+        <v>694528</v>
       </c>
       <c r="R8" t="n">
-        <v>6658762</v>
+        <v>6658686</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121762198</v>
+        <v>121761316</v>
       </c>
       <c r="B9" t="n">
-        <v>97069</v>
+        <v>57381</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,27 +1504,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1527,10 +1540,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694507</v>
+        <v>694505</v>
       </c>
       <c r="R9" t="n">
-        <v>6658692</v>
+        <v>6658779</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1581,13 +1594,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1598,17 +1610,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121765718</v>
+        <v>121753975</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,20 +1629,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1639,16 +1651,25 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694515</v>
+        <v>694530</v>
       </c>
       <c r="R10" t="n">
-        <v>6658790</v>
+        <v>6658683</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,34 +1704,25 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Stort, brett hål nära tallens bas.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1720,7 +1732,7 @@
         <v>121753760</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1824,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121761311</v>
+        <v>121765721</v>
       </c>
       <c r="B12" t="n">
-        <v>57248</v>
+        <v>97087</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,49 +1848,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100001</v>
+        <v>224363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694395</v>
+        <v>694517</v>
       </c>
       <c r="R12" t="n">
-        <v>6658801</v>
+        <v>6658684</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1905,59 +1909,45 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Tallmosse</t>
+          <t>Tallmosse/sumpskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121753973</v>
+        <v>121761311</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>57256</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,46 +1956,49 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>100001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694528</v>
+        <v>694395</v>
       </c>
       <c r="R13" t="n">
-        <v>6658686</v>
+        <v>6658801</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2032,11 +2025,26 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2045,26 +2053,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121761316</v>
+        <v>121765718</v>
       </c>
       <c r="B14" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,27 +2108,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694505</v>
+        <v>694515</v>
       </c>
       <c r="R14" t="n">
-        <v>6658779</v>
+        <v>6658790</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2142,19 +2147,14 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:55</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stort, brett hål nära tallens bas.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,18 +2168,18 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Tallmosse</t>
+          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2189,7 +2189,7 @@
         <v>121857707</v>
       </c>
       <c r="B15" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121753973</v>
+        <v>121761316</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>57381</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,46 +1397,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694528</v>
+        <v>694505</v>
       </c>
       <c r="R8" t="n">
-        <v>6658686</v>
+        <v>6658779</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,11 +1466,21 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1476,26 +1489,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121761316</v>
+        <v>121753973</v>
       </c>
       <c r="B9" t="n">
-        <v>57381</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,49 +1522,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694505</v>
+        <v>694528</v>
       </c>
       <c r="R9" t="n">
-        <v>6658779</v>
+        <v>6658686</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,21 +1588,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1596,21 +1601,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,7 +1160,7 @@
         <v>121762198</v>
       </c>
       <c r="B6" t="n">
-        <v>97087</v>
+        <v>97089</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121753743</v>
+        <v>121761316</v>
       </c>
       <c r="B7" t="n">
         <v>57381</v>
@@ -1313,23 +1313,23 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694434</v>
+        <v>694505</v>
       </c>
       <c r="R7" t="n">
-        <v>6658762</v>
+        <v>6658779</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,11 +1356,21 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,23 +1379,28 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121761316</v>
+        <v>121753760</v>
       </c>
       <c r="B8" t="n">
         <v>57381</v>
@@ -1419,27 +1434,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694505</v>
+        <v>694445</v>
       </c>
       <c r="R8" t="n">
-        <v>6658779</v>
+        <v>6658760</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,21 +1478,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1489,31 +1491,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121753973</v>
+        <v>121765721</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>97089</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,39 +1523,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>224363</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694528</v>
+        <v>694517</v>
       </c>
       <c r="R9" t="n">
-        <v>6658686</v>
+        <v>6658684</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,28 +1591,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Tallmosse/sumpskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121753975</v>
+        <v>121765718</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>57381</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,20 +1627,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1651,25 +1649,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694530</v>
+        <v>694515</v>
       </c>
       <c r="R10" t="n">
-        <v>6658683</v>
+        <v>6658790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,35 +1693,44 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stort, brett hål nära tallens bas.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121753760</v>
+        <v>121761312</v>
       </c>
       <c r="B11" t="n">
-        <v>57381</v>
+        <v>55968</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,42 +1743,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6331697</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mohare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus sylvaticus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1831</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>hårrester</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>694445</v>
+        <v>694395</v>
       </c>
       <c r="R11" t="n">
-        <v>6658760</v>
+        <v>6658801</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1807,11 +1808,26 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1820,26 +1836,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121765721</v>
+        <v>121761311</v>
       </c>
       <c r="B12" t="n">
-        <v>97087</v>
+        <v>57256</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,41 +1869,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224363</v>
+        <v>100001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Accipiter gentilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694517</v>
+        <v>694395</v>
       </c>
       <c r="R12" t="n">
-        <v>6658684</v>
+        <v>6658801</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,45 +1938,59 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121761311</v>
+        <v>121753975</v>
       </c>
       <c r="B13" t="n">
-        <v>57256</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,20 +1999,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100001</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1978,27 +2021,28 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694395</v>
+        <v>694530</v>
       </c>
       <c r="R13" t="n">
-        <v>6658801</v>
+        <v>6658683</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2025,59 +2069,40 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121765718</v>
+        <v>121753973</v>
       </c>
       <c r="B14" t="n">
-        <v>57381</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,38 +2111,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694515</v>
+        <v>694528</v>
       </c>
       <c r="R14" t="n">
-        <v>6658790</v>
+        <v>6658686</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,11 +2182,6 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stort, brett hål nära tallens bas.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2165,28 +2190,23 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121857707</v>
+        <v>121753743</v>
       </c>
       <c r="B15" t="n">
         <v>57381</v>
@@ -2220,24 +2240,27 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>694330</v>
+        <v>694434</v>
       </c>
       <c r="R15" t="n">
-        <v>6658794</v>
+        <v>6658762</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2264,19 +2287,9 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,6 +2313,123 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121857707</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57381</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>694330</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6658794</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121762198</v>
+        <v>121753975</v>
       </c>
       <c r="B6" t="n">
-        <v>97089</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,37 +1173,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224363</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694507</v>
+        <v>694530</v>
       </c>
       <c r="R6" t="n">
-        <v>6658692</v>
+        <v>6658683</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,19 +1239,9 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,30 +1254,25 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121761316</v>
+        <v>121762198</v>
       </c>
       <c r="B7" t="n">
-        <v>57381</v>
+        <v>97096</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,35 +1281,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>224363</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1323,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694505</v>
+        <v>694507</v>
       </c>
       <c r="R7" t="n">
-        <v>6658779</v>
+        <v>6658692</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1377,12 +1363,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Tallmosse</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1393,14 +1380,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121753760</v>
+        <v>121765718</v>
       </c>
       <c r="B8" t="n">
         <v>57381</v>
@@ -1434,21 +1421,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694445</v>
+        <v>694515</v>
       </c>
       <c r="R8" t="n">
-        <v>6658760</v>
+        <v>6658790</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,6 +1465,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stort, brett hål nära tallens bas.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1491,26 +1478,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121765721</v>
+        <v>121761311</v>
       </c>
       <c r="B9" t="n">
-        <v>97089</v>
+        <v>57256</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,41 +1511,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224363</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Accipiter gentilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694517</v>
+        <v>694395</v>
       </c>
       <c r="R9" t="n">
-        <v>6658684</v>
+        <v>6658801</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1580,45 +1580,59 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121765718</v>
+        <v>121753973</v>
       </c>
       <c r="B10" t="n">
-        <v>57381</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,38 +1641,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694515</v>
+        <v>694528</v>
       </c>
       <c r="R10" t="n">
-        <v>6658790</v>
+        <v>6658686</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,11 +1712,6 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Stort, brett hål nära tallens bas.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1706,31 +1720,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121761312</v>
+        <v>121753743</v>
       </c>
       <c r="B11" t="n">
-        <v>55968</v>
+        <v>57381</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,21 +1752,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6331697</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mohare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus sylvaticus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Nilsson, 1831</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,23 +1774,23 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>hårrester</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>694395</v>
+        <v>694434</v>
       </c>
       <c r="R11" t="n">
-        <v>6658801</v>
+        <v>6658762</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,26 +1817,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1836,31 +1830,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121761311</v>
+        <v>121765721</v>
       </c>
       <c r="B12" t="n">
-        <v>57256</v>
+        <v>97096</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,49 +1858,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100001</v>
+        <v>224363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694395</v>
+        <v>694517</v>
       </c>
       <c r="R12" t="n">
-        <v>6658801</v>
+        <v>6658684</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,59 +1919,45 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Tallmosse</t>
+          <t>Tallmosse/sumpskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121753975</v>
+        <v>121761316</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>57381</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,20 +1966,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2021,28 +1988,27 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694530</v>
+        <v>694505</v>
       </c>
       <c r="R13" t="n">
-        <v>6658683</v>
+        <v>6658779</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2069,40 +2035,54 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121753973</v>
+        <v>121761312</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>55968</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2111,46 +2091,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>6331697</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mohare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lepus timidus sylvaticus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Nilsson, 1831</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>hårrester</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694528</v>
+        <v>694395</v>
       </c>
       <c r="R14" t="n">
-        <v>6658686</v>
+        <v>6658801</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2177,11 +2160,26 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2190,23 +2188,28 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121753743</v>
+        <v>121753760</v>
       </c>
       <c r="B15" t="n">
         <v>57381</v>
@@ -2240,24 +2243,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>694434</v>
+        <v>694445</v>
       </c>
       <c r="R15" t="n">
-        <v>6658762</v>
+        <v>6658760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>121759133</v>
       </c>
       <c r="B5" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121753975</v>
+        <v>121762198</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>97105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,46 +1173,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>224363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694530</v>
+        <v>694507</v>
       </c>
       <c r="R6" t="n">
-        <v>6658683</v>
+        <v>6658692</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,9 +1230,19 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,25 +1255,30 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121762198</v>
+        <v>121765718</v>
       </c>
       <c r="B7" t="n">
-        <v>97096</v>
+        <v>57385</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,41 +1287,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694507</v>
+        <v>694515</v>
       </c>
       <c r="R7" t="n">
-        <v>6658692</v>
+        <v>6658790</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,19 +1348,14 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:55</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stort, brett hål nära tallens bas.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,34 +1364,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121765718</v>
+        <v>121761311</v>
       </c>
       <c r="B8" t="n">
-        <v>57381</v>
+        <v>57260</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,16 +1403,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1421,19 +1421,27 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694515</v>
+        <v>694395</v>
       </c>
       <c r="R8" t="n">
-        <v>6658790</v>
+        <v>6658801</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1460,14 +1468,24 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Stort, brett hål nära tallens bas.</t>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,28 +1499,28 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121761311</v>
+        <v>121753975</v>
       </c>
       <c r="B9" t="n">
-        <v>57256</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,20 +1529,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1533,27 +1551,28 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694395</v>
+        <v>694530</v>
       </c>
       <c r="R9" t="n">
-        <v>6658801</v>
+        <v>6658683</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1580,49 +1599,30 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
         <v>121753743</v>
       </c>
       <c r="B11" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121765721</v>
+        <v>121753760</v>
       </c>
       <c r="B12" t="n">
-        <v>97096</v>
+        <v>57385</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,38 +1858,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694517</v>
+        <v>694445</v>
       </c>
       <c r="R12" t="n">
-        <v>6658684</v>
+        <v>6658760</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,34 +1935,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Tallmosse/sumpskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121761316</v>
+        <v>121761312</v>
       </c>
       <c r="B13" t="n">
-        <v>57381</v>
+        <v>55972</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,21 +1969,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6331697</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mohare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus sylvaticus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1831</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,7 +1991,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>hårrester</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2002,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694505</v>
+        <v>694395</v>
       </c>
       <c r="R13" t="n">
-        <v>6658779</v>
+        <v>6658801</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2048,6 +2047,11 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,10 +2083,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121761312</v>
+        <v>121761316</v>
       </c>
       <c r="B14" t="n">
-        <v>55968</v>
+        <v>57385</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,21 +2099,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6331697</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mohare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepus timidus sylvaticus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Nilsson, 1831</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2117,7 +2121,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>hårrester</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2127,10 +2131,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694395</v>
+        <v>694505</v>
       </c>
       <c r="R14" t="n">
-        <v>6658801</v>
+        <v>6658779</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2173,11 +2177,6 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2209,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121753760</v>
+        <v>121765721</v>
       </c>
       <c r="B15" t="n">
-        <v>57381</v>
+        <v>97105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2221,43 +2220,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>224363</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>694445</v>
+        <v>694517</v>
       </c>
       <c r="R15" t="n">
-        <v>6658760</v>
+        <v>6658684</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2298,18 +2292,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Tallmosse/sumpskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2319,7 +2319,7 @@
         <v>121857707</v>
       </c>
       <c r="B16" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1387,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121761311</v>
+        <v>121753975</v>
       </c>
       <c r="B8" t="n">
-        <v>57260</v>
+        <v>5193</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,20 +1399,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1421,27 +1421,28 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694395</v>
+        <v>694530</v>
       </c>
       <c r="R8" t="n">
-        <v>6658801</v>
+        <v>6658683</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1468,59 +1469,40 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121753975</v>
+        <v>121761311</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>57260</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,20 +1511,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1551,28 +1533,27 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694530</v>
+        <v>694395</v>
       </c>
       <c r="R9" t="n">
-        <v>6658683</v>
+        <v>6658801</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1599,30 +1580,49 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>121759133</v>
       </c>
       <c r="B5" t="n">
-        <v>57385</v>
+        <v>57388</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121762198</v>
+        <v>121753743</v>
       </c>
       <c r="B6" t="n">
-        <v>97105</v>
+        <v>57388</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,41 +1169,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694507</v>
+        <v>694434</v>
       </c>
       <c r="R6" t="n">
-        <v>6658692</v>
+        <v>6658762</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,45 +1238,29 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1278,7 +1270,7 @@
         <v>121765718</v>
       </c>
       <c r="B7" t="n">
-        <v>57385</v>
+        <v>57388</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1387,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121753975</v>
+        <v>121765721</v>
       </c>
       <c r="B8" t="n">
-        <v>5193</v>
+        <v>97113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,43 +1395,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>224363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694530</v>
+        <v>694517</v>
       </c>
       <c r="R8" t="n">
-        <v>6658683</v>
+        <v>6658684</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,25 +1467,30 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Tallmosse/sumpskog</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121761311</v>
+        <v>121753973</v>
       </c>
       <c r="B9" t="n">
-        <v>57260</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,49 +1499,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694395</v>
+        <v>694528</v>
       </c>
       <c r="R9" t="n">
-        <v>6658801</v>
+        <v>6658686</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1580,26 +1565,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1608,31 +1578,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121753973</v>
+        <v>121761312</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>55973</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,46 +1606,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>6331697</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mohare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lepus timidus sylvaticus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Nilsson, 1831</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>hårrester</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694528</v>
+        <v>694395</v>
       </c>
       <c r="R10" t="n">
-        <v>6658686</v>
+        <v>6658801</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1707,11 +1675,26 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1720,26 +1703,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121753743</v>
+        <v>121761316</v>
       </c>
       <c r="B11" t="n">
-        <v>57385</v>
+        <v>57388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1774,23 +1762,23 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>694434</v>
+        <v>694505</v>
       </c>
       <c r="R11" t="n">
-        <v>6658762</v>
+        <v>6658779</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1817,11 +1805,21 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1830,26 +1828,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121753760</v>
+        <v>121753975</v>
       </c>
       <c r="B12" t="n">
-        <v>57385</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,20 +1861,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1880,21 +1883,25 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694445</v>
+        <v>694530</v>
       </c>
       <c r="R12" t="n">
-        <v>6658760</v>
+        <v>6658683</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,6 +1942,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1953,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121761312</v>
+        <v>121753760</v>
       </c>
       <c r="B13" t="n">
-        <v>55972</v>
+        <v>57388</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,45 +1977,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6331697</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mohare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lepus timidus sylvaticus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Nilsson, 1831</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>hårrester</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694395</v>
+        <v>694445</v>
       </c>
       <c r="R13" t="n">
-        <v>6658801</v>
+        <v>6658760</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,26 +2039,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2062,31 +2052,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121761316</v>
+        <v>121761311</v>
       </c>
       <c r="B14" t="n">
-        <v>57385</v>
+        <v>57263</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,16 +2084,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2131,10 +2116,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694505</v>
+        <v>694395</v>
       </c>
       <c r="R14" t="n">
-        <v>6658779</v>
+        <v>6658801</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2177,6 +2162,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,10 +2198,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121765721</v>
+        <v>121762198</v>
       </c>
       <c r="B15" t="n">
-        <v>97105</v>
+        <v>97113</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2244,17 +2234,17 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>694517</v>
+        <v>694507</v>
       </c>
       <c r="R15" t="n">
-        <v>6658684</v>
+        <v>6658692</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2281,9 +2271,19 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,18 +2298,18 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2319,7 +2319,7 @@
         <v>121857707</v>
       </c>
       <c r="B16" t="n">
-        <v>57385</v>
+        <v>57388</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>121759133</v>
       </c>
       <c r="B5" t="n">
-        <v>57388</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>121753743</v>
       </c>
       <c r="B6" t="n">
-        <v>57388</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121765718</v>
+        <v>121761311</v>
       </c>
       <c r="B7" t="n">
-        <v>57388</v>
+        <v>57265</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1301,19 +1301,27 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694515</v>
+        <v>694395</v>
       </c>
       <c r="R7" t="n">
-        <v>6658790</v>
+        <v>6658801</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,14 +1348,24 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Stort, brett hål nära tallens bas.</t>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,18 +1379,18 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1382,7 +1400,7 @@
         <v>121765721</v>
       </c>
       <c r="B8" t="n">
-        <v>97113</v>
+        <v>97115</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1487,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121753973</v>
+        <v>121753760</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>57390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,31 +1517,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1532,10 +1550,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694528</v>
+        <v>694445</v>
       </c>
       <c r="R9" t="n">
-        <v>6658686</v>
+        <v>6658760</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121761312</v>
+        <v>121761316</v>
       </c>
       <c r="B10" t="n">
-        <v>55973</v>
+        <v>57390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,21 +1628,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6331697</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mohare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus sylvaticus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nilsson, 1831</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1632,7 +1650,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>hårrester</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1642,10 +1660,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694395</v>
+        <v>694505</v>
       </c>
       <c r="R10" t="n">
-        <v>6658801</v>
+        <v>6658779</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1688,11 +1706,6 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121761316</v>
+        <v>121753973</v>
       </c>
       <c r="B11" t="n">
-        <v>57388</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,49 +1749,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>694505</v>
+        <v>694528</v>
       </c>
       <c r="R11" t="n">
-        <v>6658779</v>
+        <v>6658686</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1805,21 +1815,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1828,31 +1828,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121753975</v>
+        <v>121765718</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
+        <v>57390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,20 +1856,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1883,25 +1878,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694530</v>
+        <v>694515</v>
       </c>
       <c r="R12" t="n">
-        <v>6658683</v>
+        <v>6658790</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,35 +1922,44 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stort, brett hål nära tallens bas.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Tallmosse/sumpskog. Stort hål I gammal tall.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121753760</v>
+        <v>121761312</v>
       </c>
       <c r="B13" t="n">
-        <v>57388</v>
+        <v>55975</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,42 +1972,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6331697</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mohare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus sylvaticus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1831</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>hårrester</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694445</v>
+        <v>694395</v>
       </c>
       <c r="R13" t="n">
-        <v>6658760</v>
+        <v>6658801</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2039,11 +2037,26 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2052,26 +2065,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121761311</v>
+        <v>121762198</v>
       </c>
       <c r="B14" t="n">
-        <v>57263</v>
+        <v>97115</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,35 +2098,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100001</v>
+        <v>224363</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2116,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694395</v>
+        <v>694507</v>
       </c>
       <c r="R14" t="n">
-        <v>6658801</v>
+        <v>6658692</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2164,23 +2174,19 @@
           <t>14:55</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Tallmosse</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2191,17 +2197,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Jan Yngve Andersson, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121762198</v>
+        <v>121753975</v>
       </c>
       <c r="B15" t="n">
-        <v>97113</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2214,37 +2220,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224363</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>694507</v>
+        <v>694530</v>
       </c>
       <c r="R15" t="n">
-        <v>6658692</v>
+        <v>6658683</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2271,19 +2286,9 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,20 +2301,15 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2319,7 +2319,7 @@
         <v>121857707</v>
       </c>
       <c r="B16" t="n">
-        <v>57388</v>
+        <v>57390</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 59582-2024 artfynd.xlsx
+++ b/artfynd/A 59582-2024 artfynd.xlsx
@@ -1267,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121761311</v>
+        <v>121753973</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,49 +1279,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694395</v>
+        <v>694528</v>
       </c>
       <c r="R7" t="n">
-        <v>6658801</v>
+        <v>6658686</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,26 +1345,11 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1376,31 +1358,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121765721</v>
+        <v>121761312</v>
       </c>
       <c r="B8" t="n">
-        <v>97115</v>
+        <v>55975</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,41 +1386,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224363</v>
+        <v>6331697</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Mohare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Lepus timidus sylvaticus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Nilsson, 1831</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>hårrester</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vickelsjön, NNO-NO om, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694517</v>
+        <v>694395</v>
       </c>
       <c r="R8" t="n">
-        <v>6658684</v>
+        <v>6658801</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,45 +1455,59 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Tallmosse/sumpskog</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121753760</v>
+        <v>121761311</v>
       </c>
       <c r="B9" t="n">
-        <v>57390</v>
+        <v>57265</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,16 +1520,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1539,24 +1538,27 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694445</v>
+        <v>694395</v>
       </c>
       <c r="R9" t="n">
-        <v>6658760</v>
+        <v>6658801</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,11 +1585,26 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1596,26 +1613,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121761316</v>
+        <v>121765721</v>
       </c>
       <c r="B10" t="n">
-        <v>57390</v>
+        <v>97115</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,49 +1646,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>224363</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Vickelsjön, NNO-NO om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>694505</v>
+        <v>694517</v>
       </c>
       <c r="R10" t="n">
-        <v>6658779</v>
+        <v>6658684</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1693,54 +1707,45 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Tallmosse</t>
+          <t>Tallmosse/sumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121753973</v>
+        <v>121762198</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>97115</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,42 +1758,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>224363</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
+          <t>mellan Vickelsjön och Storsjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>694528</v>
+        <v>694507</v>
       </c>
       <c r="R11" t="n">
-        <v>6658686</v>
+        <v>6658692</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1815,29 +1815,45 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1956,10 +1972,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121761312</v>
+        <v>121761316</v>
       </c>
       <c r="B13" t="n">
-        <v>55975</v>
+        <v>57390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1972,21 +1988,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6331697</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mohare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lepus timidus sylvaticus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Nilsson, 1831</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1994,7 +2010,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>hårrester</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2004,10 +2020,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694395</v>
+        <v>694505</v>
       </c>
       <c r="R13" t="n">
-        <v>6658801</v>
+        <v>6658779</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2050,11 +2066,6 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Slagen skogshare/mohare med pälsrester. Spillningsutsprut ses kl 20 vilket indikerar att en en rovfågel slagit den och allt tyder på duvhök.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121762198</v>
+        <v>121753975</v>
       </c>
       <c r="B14" t="n">
-        <v>97115</v>
+        <v>5193</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2102,37 +2113,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224363</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>mellan Vickelsjön och Storsjön, Upl</t>
+          <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694507</v>
+        <v>694530</v>
       </c>
       <c r="R14" t="n">
-        <v>6658692</v>
+        <v>6658683</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2159,19 +2179,9 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,30 +2194,25 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Jan Yngve Andersson, Joakim Ekman</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121753975</v>
+        <v>121753760</v>
       </c>
       <c r="B15" t="n">
-        <v>5193</v>
+        <v>57390</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,20 +2221,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2238,25 +2243,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sko-Lassesholmen, Sko-Lassesholmen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>694530</v>
+        <v>694445</v>
       </c>
       <c r="R15" t="n">
-        <v>6658683</v>
+        <v>6658760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2297,7 +2298,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
